--- a/initial_descriptive_analysis/output/sample_description/csv/sociodemographic_by_archetype_for_word.xlsx
+++ b/initial_descriptive_analysis/output/sample_description/csv/sociodemographic_by_archetype_for_word.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
   <si>
     <t xml:space="preserve">characteristic</t>
   </si>
@@ -110,7 +110,7 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">  Boomers + generación silenciosa</t>
+    <t xml:space="preserve">  Boomers +</t>
   </si>
   <si>
     <t xml:space="preserve">105 (27.1%)</t>
@@ -608,259 +608,235 @@
     <t xml:space="preserve">14 (40.0%)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Otro tipo de hogar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (1.3%)</t>
+    <t xml:space="preserve">  Otros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83 (21.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (17.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (19.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 (16.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (20.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (37.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Pareja sin hijos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126 (33.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37 (49.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (35.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 (28.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (25.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 (22.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Régimen de tenencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  No propietarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102 (25.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34 (43.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 (18.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 (32.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 (38.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (7.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (8.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Propiedad con hipoteca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109 (27.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 (24.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 (37.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (22.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 (27.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Propiedad sin hipoteca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185 (46.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 (32.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 (44.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 (45.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 (64.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (68.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zona climática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Clima cálido/mediterráneo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160 (39.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 (23.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (33.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 (58.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (20.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 (40.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 (80.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Clima frío/polar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 (4.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (7.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (2.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (5.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (1.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Clima templado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">226 (56.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57 (69.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 (63.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 (35.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47 (78.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 (56.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Otro clima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orientación política</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Centro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73 (19.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 (29.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 (17.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 (16.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 (36.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">2 (3.7%)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Pareja sin hijos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126 (33.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37 (49.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (35.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 (28.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (25.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (22.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Vive solo/a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70 (18.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (17.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (16.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (17.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 (12.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (16.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Vivienda compartida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (2.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (6.7%)</t>
+    <t xml:space="preserve">  Derecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 (7.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (8.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 (15.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 (8.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (1.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Extrema derecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 (1.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (4.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">1 (1.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Régimen de tenencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Alquiler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88 (22.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32 (40.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 (29.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (31.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (1.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (8.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Otro régimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 (3.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (2.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (6.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (5.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Propiedad con hipoteca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109 (27.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (24.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 (37.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (22.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 (27.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Propiedad sin hipoteca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185 (46.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26 (32.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 (44.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 (45.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35 (64.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (68.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zona climática</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Clima cálido/mediterráneo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160 (39.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 (23.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (33.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40 (58.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (20.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 (40.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28 (80.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Clima frío/polar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 (4.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (7.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 (2.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (5.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 (1.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Clima templado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">226 (56.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57 (69.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45 (63.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 (35.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47 (78.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 (56.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Otro clima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orientación política</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Centro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73 (19.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 (29.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (17.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 (16.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 (36.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Derecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 (7.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (8.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 (15.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 (8.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Extrema derecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 (1.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 (4.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">  Extrema izquierda</t>
@@ -3889,28 +3865,28 @@
         <v>198</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>199</v>
       </c>
       <c r="C84" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D84" t="s">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E84" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="F84" t="s">
-        <v>87</v>
+        <v>202</v>
       </c>
       <c r="G84" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H84" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="I84" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="J84" t="s">
         <v>40</v>
@@ -3918,28 +3894,28 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B85" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C85" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D85" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E85" t="s">
         <v>61</v>
       </c>
       <c r="F85" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G85" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="H85" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I85" t="s">
         <v>88</v>
@@ -3950,28 +3926,28 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="B86" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="C86" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="D86" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="E86" t="s">
-        <v>212</v>
+        <v>79</v>
       </c>
       <c r="F86" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="G86" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="H86" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="I86" t="s">
         <v>65</v>
@@ -3982,31 +3958,31 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="B87" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="C87" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="D87" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="E87" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="F87" t="s">
-        <v>87</v>
+        <v>202</v>
       </c>
       <c r="G87" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="H87" t="s">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="I87" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="J87" t="s">
         <v>40</v>
@@ -4014,63 +3990,63 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B88" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="C88" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="D88" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="E88" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F88" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="G88" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="H88" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="I88" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="J88" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B89" t="s">
-        <v>85</v>
+        <v>192</v>
       </c>
       <c r="C89" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D89" t="s">
-        <v>40</v>
+        <v>194</v>
       </c>
       <c r="E89" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="F89" t="s">
-        <v>87</v>
+        <v>195</v>
       </c>
       <c r="G89" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H89" t="s">
-        <v>40</v>
+        <v>197</v>
       </c>
       <c r="I89" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="J89" t="s">
         <v>40</v>
@@ -4078,159 +4054,159 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>198</v>
+      </c>
+      <c r="B90" t="s">
+        <v>199</v>
+      </c>
+      <c r="C90" t="s">
+        <v>193</v>
+      </c>
+      <c r="D90" t="s">
+        <v>200</v>
+      </c>
+      <c r="E90" t="s">
         <v>201</v>
       </c>
-      <c r="B90" t="s">
+      <c r="F90" t="s">
         <v>202</v>
       </c>
-      <c r="C90" t="s">
+      <c r="G90" t="s">
         <v>203</v>
       </c>
-      <c r="D90" t="s">
+      <c r="H90" t="s">
         <v>204</v>
       </c>
-      <c r="E90" t="s">
-        <v>61</v>
-      </c>
-      <c r="F90" t="s">
-        <v>205</v>
-      </c>
-      <c r="G90" t="s">
-        <v>206</v>
-      </c>
-      <c r="H90" t="s">
-        <v>207</v>
-      </c>
       <c r="I90" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="J90" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
+        <v>205</v>
+      </c>
+      <c r="B91" t="s">
+        <v>206</v>
+      </c>
+      <c r="C91" t="s">
+        <v>207</v>
+      </c>
+      <c r="D91" t="s">
         <v>208</v>
       </c>
-      <c r="B91" t="s">
+      <c r="E91" t="s">
+        <v>61</v>
+      </c>
+      <c r="F91" t="s">
         <v>209</v>
       </c>
-      <c r="C91" t="s">
+      <c r="G91" t="s">
         <v>210</v>
       </c>
-      <c r="D91" t="s">
+      <c r="H91" t="s">
         <v>211</v>
       </c>
-      <c r="E91" t="s">
-        <v>212</v>
-      </c>
-      <c r="F91" t="s">
-        <v>213</v>
-      </c>
-      <c r="G91" t="s">
-        <v>214</v>
-      </c>
-      <c r="H91" t="s">
-        <v>143</v>
-      </c>
       <c r="I91" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="J91" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B92" t="s">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>217</v>
+        <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="E92" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="F92" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="G92" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H92" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="I92" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J92" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C93" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="D93" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="E93" t="s">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="F93" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="G93" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="H93" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="I93" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="J93" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="B94" t="s">
-        <v>85</v>
+        <v>222</v>
       </c>
       <c r="C94" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="D94" t="s">
-        <v>40</v>
+        <v>224</v>
       </c>
       <c r="E94" t="s">
-        <v>40</v>
+        <v>225</v>
       </c>
       <c r="F94" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="G94" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="H94" t="s">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="I94" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J94" t="s">
         <v>40</v>
@@ -4238,95 +4214,95 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="B95" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="C95" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="D95" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="E95" t="s">
-        <v>61</v>
+        <v>231</v>
       </c>
       <c r="F95" t="s">
-        <v>205</v>
+        <v>113</v>
       </c>
       <c r="G95" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="H95" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="I95" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="J95" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B96" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C96" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D96" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E96" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F96" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G96" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H96" t="s">
-        <v>143</v>
+        <v>220</v>
       </c>
       <c r="I96" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="J96" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B97" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C97" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D97" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E97" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="G97" t="s">
-        <v>40</v>
+        <v>226</v>
       </c>
       <c r="H97" t="s">
-        <v>115</v>
+        <v>211</v>
       </c>
       <c r="I97" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J97" t="s">
         <v>40</v>
@@ -4334,31 +4310,31 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="B98" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="C98" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="D98" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="E98" t="s">
-        <v>79</v>
+        <v>231</v>
       </c>
       <c r="F98" t="s">
-        <v>195</v>
+        <v>113</v>
       </c>
       <c r="G98" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="H98" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="I98" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="J98" t="s">
         <v>40</v>
@@ -4366,95 +4342,95 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B99" t="s">
-        <v>85</v>
+        <v>214</v>
       </c>
       <c r="C99" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="D99" t="s">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="E99" t="s">
-        <v>40</v>
+        <v>217</v>
       </c>
       <c r="F99" t="s">
-        <v>87</v>
+        <v>218</v>
       </c>
       <c r="G99" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="H99" t="s">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c r="I99" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="J99" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="B100" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="C100" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="D100" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="E100" t="s">
-        <v>61</v>
+        <v>225</v>
       </c>
       <c r="F100" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="G100" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="H100" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I100" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="J100" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="B101" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C101" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="D101" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="E101" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="F101" t="s">
-        <v>213</v>
+        <v>113</v>
       </c>
       <c r="G101" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="H101" t="s">
-        <v>143</v>
+        <v>233</v>
       </c>
       <c r="I101" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="J101" t="s">
         <v>40</v>
@@ -4462,63 +4438,63 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="B102" t="s">
-        <v>216</v>
+        <v>31</v>
       </c>
       <c r="C102" t="s">
-        <v>217</v>
+        <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="E102" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="F102" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="G102" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H102" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="I102" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J102" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="B103" t="s">
-        <v>192</v>
+        <v>236</v>
       </c>
       <c r="C103" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="D103" t="s">
-        <v>194</v>
+        <v>238</v>
       </c>
       <c r="E103" t="s">
-        <v>79</v>
+        <v>239</v>
       </c>
       <c r="F103" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="G103" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="H103" t="s">
-        <v>197</v>
+        <v>242</v>
       </c>
       <c r="I103" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="J103" t="s">
         <v>40</v>
@@ -4526,31 +4502,31 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>198</v>
+        <v>243</v>
       </c>
       <c r="B104" t="s">
-        <v>85</v>
+        <v>244</v>
       </c>
       <c r="C104" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="D104" t="s">
-        <v>40</v>
+        <v>246</v>
       </c>
       <c r="E104" t="s">
-        <v>40</v>
+        <v>247</v>
       </c>
       <c r="F104" t="s">
-        <v>87</v>
+        <v>248</v>
       </c>
       <c r="G104" t="s">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="H104" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="I104" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="J104" t="s">
         <v>40</v>
@@ -4558,31 +4534,31 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="B105" t="s">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="C105" t="s">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="D105" t="s">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="E105" t="s">
-        <v>61</v>
+        <v>253</v>
       </c>
       <c r="F105" t="s">
-        <v>205</v>
+        <v>254</v>
       </c>
       <c r="G105" t="s">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="H105" t="s">
-        <v>207</v>
+        <v>64</v>
       </c>
       <c r="I105" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="J105" t="s">
         <v>66</v>
@@ -4590,31 +4566,31 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>208</v>
+        <v>256</v>
       </c>
       <c r="B106" t="s">
-        <v>209</v>
+        <v>40</v>
       </c>
       <c r="C106" t="s">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="D106" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="E106" t="s">
-        <v>212</v>
+        <v>40</v>
       </c>
       <c r="F106" t="s">
-        <v>213</v>
+        <v>40</v>
       </c>
       <c r="G106" t="s">
-        <v>214</v>
+        <v>40</v>
       </c>
       <c r="H106" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="I106" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J106" t="s">
         <v>40</v>
@@ -4622,31 +4598,31 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="B107" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="C107" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="D107" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="E107" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="F107" t="s">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="G107" t="s">
-        <v>40</v>
+        <v>241</v>
       </c>
       <c r="H107" t="s">
-        <v>115</v>
+        <v>242</v>
       </c>
       <c r="I107" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J107" t="s">
         <v>40</v>
@@ -4654,89 +4630,89 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="B108" t="s">
-        <v>31</v>
+        <v>244</v>
       </c>
       <c r="C108" t="s">
-        <v>31</v>
+        <v>245</v>
       </c>
       <c r="D108" t="s">
-        <v>31</v>
+        <v>246</v>
       </c>
       <c r="E108" t="s">
-        <v>31</v>
+        <v>247</v>
       </c>
       <c r="F108" t="s">
-        <v>31</v>
+        <v>248</v>
       </c>
       <c r="G108" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H108" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="I108" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="J108" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="B109" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="C109" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="D109" t="s">
-        <v>125</v>
+        <v>252</v>
       </c>
       <c r="E109" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="F109" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="G109" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="H109" t="s">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="I109" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="J109" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="B110" t="s">
-        <v>228</v>
+        <v>40</v>
       </c>
       <c r="C110" t="s">
-        <v>229</v>
+        <v>40</v>
       </c>
       <c r="D110" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="E110" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="F110" t="s">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="G110" t="s">
-        <v>231</v>
+        <v>40</v>
       </c>
       <c r="H110" t="s">
         <v>40</v>
@@ -4745,33 +4721,33 @@
         <v>40</v>
       </c>
       <c r="J110" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B111" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C111" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D111" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E111" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F111" t="s">
-        <v>132</v>
+        <v>240</v>
       </c>
       <c r="G111" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H111" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="I111" t="s">
         <v>57</v>
@@ -4782,31 +4758,31 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B112" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C112" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D112" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E112" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F112" t="s">
-        <v>113</v>
+        <v>248</v>
       </c>
       <c r="G112" t="s">
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="H112" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="I112" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="J112" t="s">
         <v>40</v>
@@ -4814,57 +4790,57 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="B113" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="C113" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="D113" t="s">
-        <v>125</v>
+        <v>252</v>
       </c>
       <c r="E113" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="F113" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="G113" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="H113" t="s">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="I113" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="J113" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="B114" t="s">
-        <v>228</v>
+        <v>40</v>
       </c>
       <c r="C114" t="s">
-        <v>229</v>
+        <v>40</v>
       </c>
       <c r="D114" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="E114" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="F114" t="s">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="G114" t="s">
-        <v>231</v>
+        <v>40</v>
       </c>
       <c r="H114" t="s">
         <v>40</v>
@@ -4873,33 +4849,33 @@
         <v>40</v>
       </c>
       <c r="J114" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B115" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C115" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D115" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E115" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F115" t="s">
-        <v>132</v>
+        <v>240</v>
       </c>
       <c r="G115" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H115" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="I115" t="s">
         <v>57</v>
@@ -4910,31 +4886,31 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C116" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D116" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E116" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F116" t="s">
-        <v>113</v>
+        <v>248</v>
       </c>
       <c r="G116" t="s">
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="H116" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="I116" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="J116" t="s">
         <v>40</v>
@@ -4942,57 +4918,57 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="B117" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="C117" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="D117" t="s">
-        <v>125</v>
+        <v>252</v>
       </c>
       <c r="E117" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="F117" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="G117" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="H117" t="s">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="I117" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="J117" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="B118" t="s">
-        <v>228</v>
+        <v>40</v>
       </c>
       <c r="C118" t="s">
-        <v>229</v>
+        <v>40</v>
       </c>
       <c r="D118" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="E118" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="F118" t="s">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="G118" t="s">
-        <v>231</v>
+        <v>40</v>
       </c>
       <c r="H118" t="s">
         <v>40</v>
@@ -5001,68 +4977,68 @@
         <v>40</v>
       </c>
       <c r="J118" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="B119" t="s">
-        <v>233</v>
+        <v>31</v>
       </c>
       <c r="C119" t="s">
-        <v>234</v>
+        <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>235</v>
+        <v>31</v>
       </c>
       <c r="E119" t="s">
-        <v>236</v>
+        <v>31</v>
       </c>
       <c r="F119" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="G119" t="s">
-        <v>237</v>
+        <v>31</v>
       </c>
       <c r="H119" t="s">
-        <v>207</v>
+        <v>31</v>
       </c>
       <c r="I119" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="J119" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="B120" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C120" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="E120" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="F120" t="s">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="G120" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="H120" t="s">
-        <v>244</v>
+        <v>127</v>
       </c>
       <c r="I120" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="J120" t="s">
         <v>40</v>
@@ -5070,28 +5046,28 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>220</v>
+        <v>265</v>
       </c>
       <c r="B121" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="C121" t="s">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>125</v>
+        <v>247</v>
       </c>
       <c r="E121" t="s">
-        <v>223</v>
+        <v>268</v>
       </c>
       <c r="F121" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="G121" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="H121" t="s">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="I121" t="s">
         <v>88</v>
@@ -5102,25 +5078,25 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="B122" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="C122" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="D122" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="E122" t="s">
-        <v>86</v>
+        <v>274</v>
       </c>
       <c r="F122" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="G122" t="s">
-        <v>231</v>
+        <v>40</v>
       </c>
       <c r="H122" t="s">
         <v>40</v>
@@ -5129,68 +5105,68 @@
         <v>40</v>
       </c>
       <c r="J122" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="B123" t="s">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="C123" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="D123" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="E123" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="F123" t="s">
-        <v>132</v>
+        <v>278</v>
       </c>
       <c r="G123" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="H123" t="s">
-        <v>207</v>
+        <v>280</v>
       </c>
       <c r="I123" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="J123" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>238</v>
+        <v>281</v>
       </c>
       <c r="B124" t="s">
-        <v>239</v>
+        <v>282</v>
       </c>
       <c r="C124" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="D124" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="E124" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="F124" t="s">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="G124" t="s">
-        <v>243</v>
+        <v>286</v>
       </c>
       <c r="H124" t="s">
-        <v>244</v>
+        <v>287</v>
       </c>
       <c r="I124" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="J124" t="s">
         <v>40</v>
@@ -5198,63 +5174,63 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>31</v>
+        <v>259</v>
       </c>
       <c r="C125" t="s">
-        <v>31</v>
+        <v>260</v>
       </c>
       <c r="D125" t="s">
-        <v>31</v>
+        <v>261</v>
       </c>
       <c r="E125" t="s">
-        <v>31</v>
+        <v>262</v>
       </c>
       <c r="F125" t="s">
-        <v>31</v>
+        <v>263</v>
       </c>
       <c r="G125" t="s">
-        <v>31</v>
+        <v>264</v>
       </c>
       <c r="H125" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="I125" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="J125" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="B126" t="s">
+        <v>266</v>
+      </c>
+      <c r="C126" t="s">
+        <v>267</v>
+      </c>
+      <c r="D126" t="s">
         <v>247</v>
       </c>
-      <c r="C126" t="s">
-        <v>248</v>
-      </c>
-      <c r="D126" t="s">
-        <v>249</v>
-      </c>
       <c r="E126" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="F126" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="G126" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="H126" t="s">
-        <v>253</v>
+        <v>115</v>
       </c>
       <c r="I126" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="J126" t="s">
         <v>40</v>
@@ -5262,31 +5238,31 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B127" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C127" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="D127" t="s">
-        <v>257</v>
+        <v>40</v>
       </c>
       <c r="E127" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="F127" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="G127" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="H127" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="I127" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="J127" t="s">
         <v>40</v>
@@ -5294,31 +5270,31 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
+        <v>275</v>
+      </c>
+      <c r="B128" t="s">
+        <v>276</v>
+      </c>
+      <c r="C128" t="s">
         <v>260</v>
       </c>
-      <c r="B128" t="s">
-        <v>261</v>
-      </c>
-      <c r="C128" t="s">
-        <v>262</v>
-      </c>
       <c r="D128" t="s">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="E128" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="F128" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="G128" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="H128" t="s">
-        <v>64</v>
+        <v>280</v>
       </c>
       <c r="I128" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="J128" t="s">
         <v>66</v>
@@ -5326,31 +5302,31 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B129" t="s">
-        <v>40</v>
+        <v>282</v>
       </c>
       <c r="C129" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="D129" t="s">
-        <v>40</v>
+        <v>283</v>
       </c>
       <c r="E129" t="s">
-        <v>40</v>
+        <v>284</v>
       </c>
       <c r="F129" t="s">
-        <v>40</v>
+        <v>285</v>
       </c>
       <c r="G129" t="s">
-        <v>40</v>
+        <v>286</v>
       </c>
       <c r="H129" t="s">
-        <v>40</v>
+        <v>287</v>
       </c>
       <c r="I129" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J129" t="s">
         <v>40</v>
@@ -5358,31 +5334,31 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B130" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D130" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E130" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="F130" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="G130" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="H130" t="s">
-        <v>253</v>
+        <v>127</v>
       </c>
       <c r="I130" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="J130" t="s">
         <v>40</v>
@@ -5390,25 +5366,25 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B131" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C131" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="D131" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="E131" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="F131" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G131" t="s">
-        <v>56</v>
+        <v>270</v>
       </c>
       <c r="H131" t="s">
         <v>115</v>
@@ -5422,92 +5398,92 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B132" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C132" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D132" t="s">
-        <v>263</v>
+        <v>40</v>
       </c>
       <c r="E132" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="F132" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="G132" t="s">
-        <v>266</v>
+        <v>40</v>
       </c>
       <c r="H132" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="I132" t="s">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="J132" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B133" t="s">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="C133" t="s">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="D133" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="E133" t="s">
-        <v>40</v>
+        <v>277</v>
       </c>
       <c r="F133" t="s">
-        <v>40</v>
+        <v>278</v>
       </c>
       <c r="G133" t="s">
-        <v>40</v>
+        <v>279</v>
       </c>
       <c r="H133" t="s">
-        <v>40</v>
+        <v>280</v>
       </c>
       <c r="I133" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="J133" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>246</v>
+        <v>281</v>
       </c>
       <c r="B134" t="s">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="C134" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D134" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="E134" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="F134" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="G134" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="H134" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="I134" t="s">
         <v>57</v>
@@ -5518,28 +5494,28 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B135" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D135" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E135" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F135" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="G135" t="s">
-        <v>56</v>
+        <v>264</v>
       </c>
       <c r="H135" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="I135" t="s">
         <v>88</v>
@@ -5550,54 +5526,54 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B136" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D136" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="E136" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F136" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G136" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H136" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="I136" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="J136" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B137" t="s">
-        <v>40</v>
+        <v>272</v>
       </c>
       <c r="C137" t="s">
-        <v>40</v>
+        <v>273</v>
       </c>
       <c r="D137" t="s">
         <v>40</v>
       </c>
       <c r="E137" t="s">
-        <v>40</v>
+        <v>274</v>
       </c>
       <c r="F137" t="s">
-        <v>40</v>
+        <v>248</v>
       </c>
       <c r="G137" t="s">
         <v>40</v>
@@ -5614,63 +5590,63 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="B138" t="s">
-        <v>247</v>
+        <v>276</v>
       </c>
       <c r="C138" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="D138" t="s">
-        <v>249</v>
+        <v>78</v>
       </c>
       <c r="E138" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="F138" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="G138" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="H138" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="I138" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="J138" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="B139" t="s">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="C139" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D139" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="E139" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="F139" t="s">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="G139" t="s">
-        <v>56</v>
+        <v>286</v>
       </c>
       <c r="H139" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="I139" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="J139" t="s">
         <v>40</v>
@@ -5678,63 +5654,63 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
+        <v>258</v>
+      </c>
+      <c r="B140" t="s">
+        <v>259</v>
+      </c>
+      <c r="C140" t="s">
         <v>260</v>
       </c>
-      <c r="B140" t="s">
+      <c r="D140" t="s">
         <v>261</v>
       </c>
-      <c r="C140" t="s">
+      <c r="E140" t="s">
         <v>262</v>
       </c>
-      <c r="D140" t="s">
+      <c r="F140" t="s">
         <v>263</v>
       </c>
-      <c r="E140" t="s">
+      <c r="G140" t="s">
         <v>264</v>
       </c>
-      <c r="F140" t="s">
-        <v>265</v>
-      </c>
-      <c r="G140" t="s">
-        <v>266</v>
-      </c>
       <c r="H140" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="I140" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="J140" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
+        <v>265</v>
+      </c>
+      <c r="B141" t="s">
+        <v>266</v>
+      </c>
+      <c r="C141" t="s">
         <v>267</v>
       </c>
-      <c r="B141" t="s">
-        <v>40</v>
-      </c>
-      <c r="C141" t="s">
-        <v>40</v>
-      </c>
       <c r="D141" t="s">
-        <v>40</v>
+        <v>247</v>
       </c>
       <c r="E141" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="F141" t="s">
-        <v>40</v>
+        <v>269</v>
       </c>
       <c r="G141" t="s">
-        <v>40</v>
+        <v>270</v>
       </c>
       <c r="H141" t="s">
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="I141" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="J141" t="s">
         <v>40</v>
@@ -5742,833 +5718,97 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B142" t="s">
-        <v>31</v>
+        <v>272</v>
       </c>
       <c r="C142" t="s">
-        <v>31</v>
+        <v>273</v>
       </c>
       <c r="D142" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E142" t="s">
-        <v>31</v>
+        <v>274</v>
       </c>
       <c r="F142" t="s">
-        <v>31</v>
+        <v>248</v>
       </c>
       <c r="G142" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H142" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I142" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J142" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B143" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C143" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="D143" t="s">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="E143" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F143" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G143" t="s">
-        <v>200</v>
+        <v>279</v>
       </c>
       <c r="H143" t="s">
-        <v>127</v>
+        <v>280</v>
       </c>
       <c r="I143" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J143" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B144" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C144" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="E144" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F144" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G144" t="s">
-        <v>225</v>
+        <v>286</v>
       </c>
       <c r="H144" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="I144" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="J144" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>280</v>
-      </c>
-      <c r="B145" t="s">
-        <v>281</v>
-      </c>
-      <c r="C145" t="s">
-        <v>282</v>
-      </c>
-      <c r="D145" t="s">
-        <v>40</v>
-      </c>
-      <c r="E145" t="s">
-        <v>218</v>
-      </c>
-      <c r="F145" t="s">
-        <v>259</v>
-      </c>
-      <c r="G145" t="s">
-        <v>40</v>
-      </c>
-      <c r="H145" t="s">
-        <v>40</v>
-      </c>
-      <c r="I145" t="s">
-        <v>40</v>
-      </c>
-      <c r="J145" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>283</v>
-      </c>
-      <c r="B146" t="s">
-        <v>284</v>
-      </c>
-      <c r="C146" t="s">
-        <v>271</v>
-      </c>
-      <c r="D146" t="s">
-        <v>78</v>
-      </c>
-      <c r="E146" t="s">
-        <v>285</v>
-      </c>
-      <c r="F146" t="s">
-        <v>286</v>
-      </c>
-      <c r="G146" t="s">
-        <v>287</v>
-      </c>
-      <c r="H146" t="s">
-        <v>288</v>
-      </c>
-      <c r="I146" t="s">
-        <v>83</v>
-      </c>
-      <c r="J146" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>289</v>
-      </c>
-      <c r="B147" t="s">
-        <v>290</v>
-      </c>
-      <c r="C147" t="s">
-        <v>271</v>
-      </c>
-      <c r="D147" t="s">
-        <v>291</v>
-      </c>
-      <c r="E147" t="s">
-        <v>292</v>
-      </c>
-      <c r="F147" t="s">
-        <v>293</v>
-      </c>
-      <c r="G147" t="s">
-        <v>294</v>
-      </c>
-      <c r="H147" t="s">
-        <v>295</v>
-      </c>
-      <c r="I147" t="s">
-        <v>57</v>
-      </c>
-      <c r="J147" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>269</v>
-      </c>
-      <c r="B148" t="s">
-        <v>270</v>
-      </c>
-      <c r="C148" t="s">
-        <v>271</v>
-      </c>
-      <c r="D148" t="s">
-        <v>272</v>
-      </c>
-      <c r="E148" t="s">
-        <v>273</v>
-      </c>
-      <c r="F148" t="s">
-        <v>274</v>
-      </c>
-      <c r="G148" t="s">
-        <v>200</v>
-      </c>
-      <c r="H148" t="s">
-        <v>127</v>
-      </c>
-      <c r="I148" t="s">
-        <v>88</v>
-      </c>
-      <c r="J148" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>275</v>
-      </c>
-      <c r="B149" t="s">
-        <v>276</v>
-      </c>
-      <c r="C149" t="s">
-        <v>277</v>
-      </c>
-      <c r="D149" t="s">
-        <v>258</v>
-      </c>
-      <c r="E149" t="s">
-        <v>278</v>
-      </c>
-      <c r="F149" t="s">
-        <v>279</v>
-      </c>
-      <c r="G149" t="s">
-        <v>225</v>
-      </c>
-      <c r="H149" t="s">
-        <v>115</v>
-      </c>
-      <c r="I149" t="s">
-        <v>88</v>
-      </c>
-      <c r="J149" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>280</v>
-      </c>
-      <c r="B150" t="s">
-        <v>281</v>
-      </c>
-      <c r="C150" t="s">
-        <v>282</v>
-      </c>
-      <c r="D150" t="s">
-        <v>40</v>
-      </c>
-      <c r="E150" t="s">
-        <v>218</v>
-      </c>
-      <c r="F150" t="s">
-        <v>259</v>
-      </c>
-      <c r="G150" t="s">
-        <v>40</v>
-      </c>
-      <c r="H150" t="s">
-        <v>40</v>
-      </c>
-      <c r="I150" t="s">
-        <v>40</v>
-      </c>
-      <c r="J150" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>283</v>
-      </c>
-      <c r="B151" t="s">
-        <v>284</v>
-      </c>
-      <c r="C151" t="s">
-        <v>271</v>
-      </c>
-      <c r="D151" t="s">
-        <v>78</v>
-      </c>
-      <c r="E151" t="s">
-        <v>285</v>
-      </c>
-      <c r="F151" t="s">
-        <v>286</v>
-      </c>
-      <c r="G151" t="s">
-        <v>287</v>
-      </c>
-      <c r="H151" t="s">
-        <v>288</v>
-      </c>
-      <c r="I151" t="s">
-        <v>83</v>
-      </c>
-      <c r="J151" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>289</v>
-      </c>
-      <c r="B152" t="s">
-        <v>290</v>
-      </c>
-      <c r="C152" t="s">
-        <v>271</v>
-      </c>
-      <c r="D152" t="s">
-        <v>291</v>
-      </c>
-      <c r="E152" t="s">
-        <v>292</v>
-      </c>
-      <c r="F152" t="s">
-        <v>293</v>
-      </c>
-      <c r="G152" t="s">
-        <v>294</v>
-      </c>
-      <c r="H152" t="s">
-        <v>295</v>
-      </c>
-      <c r="I152" t="s">
-        <v>57</v>
-      </c>
-      <c r="J152" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>269</v>
-      </c>
-      <c r="B153" t="s">
-        <v>270</v>
-      </c>
-      <c r="C153" t="s">
-        <v>271</v>
-      </c>
-      <c r="D153" t="s">
-        <v>272</v>
-      </c>
-      <c r="E153" t="s">
-        <v>273</v>
-      </c>
-      <c r="F153" t="s">
-        <v>274</v>
-      </c>
-      <c r="G153" t="s">
-        <v>200</v>
-      </c>
-      <c r="H153" t="s">
-        <v>127</v>
-      </c>
-      <c r="I153" t="s">
-        <v>88</v>
-      </c>
-      <c r="J153" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>275</v>
-      </c>
-      <c r="B154" t="s">
-        <v>276</v>
-      </c>
-      <c r="C154" t="s">
-        <v>277</v>
-      </c>
-      <c r="D154" t="s">
-        <v>258</v>
-      </c>
-      <c r="E154" t="s">
-        <v>278</v>
-      </c>
-      <c r="F154" t="s">
-        <v>279</v>
-      </c>
-      <c r="G154" t="s">
-        <v>225</v>
-      </c>
-      <c r="H154" t="s">
-        <v>115</v>
-      </c>
-      <c r="I154" t="s">
-        <v>88</v>
-      </c>
-      <c r="J154" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>280</v>
-      </c>
-      <c r="B155" t="s">
-        <v>281</v>
-      </c>
-      <c r="C155" t="s">
-        <v>282</v>
-      </c>
-      <c r="D155" t="s">
-        <v>40</v>
-      </c>
-      <c r="E155" t="s">
-        <v>218</v>
-      </c>
-      <c r="F155" t="s">
-        <v>259</v>
-      </c>
-      <c r="G155" t="s">
-        <v>40</v>
-      </c>
-      <c r="H155" t="s">
-        <v>40</v>
-      </c>
-      <c r="I155" t="s">
-        <v>40</v>
-      </c>
-      <c r="J155" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>283</v>
-      </c>
-      <c r="B156" t="s">
-        <v>284</v>
-      </c>
-      <c r="C156" t="s">
-        <v>271</v>
-      </c>
-      <c r="D156" t="s">
-        <v>78</v>
-      </c>
-      <c r="E156" t="s">
-        <v>285</v>
-      </c>
-      <c r="F156" t="s">
-        <v>286</v>
-      </c>
-      <c r="G156" t="s">
-        <v>287</v>
-      </c>
-      <c r="H156" t="s">
-        <v>288</v>
-      </c>
-      <c r="I156" t="s">
-        <v>83</v>
-      </c>
-      <c r="J156" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>289</v>
-      </c>
-      <c r="B157" t="s">
-        <v>290</v>
-      </c>
-      <c r="C157" t="s">
-        <v>271</v>
-      </c>
-      <c r="D157" t="s">
-        <v>291</v>
-      </c>
-      <c r="E157" t="s">
-        <v>292</v>
-      </c>
-      <c r="F157" t="s">
-        <v>293</v>
-      </c>
-      <c r="G157" t="s">
-        <v>294</v>
-      </c>
-      <c r="H157" t="s">
-        <v>295</v>
-      </c>
-      <c r="I157" t="s">
-        <v>57</v>
-      </c>
-      <c r="J157" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>269</v>
-      </c>
-      <c r="B158" t="s">
-        <v>270</v>
-      </c>
-      <c r="C158" t="s">
-        <v>271</v>
-      </c>
-      <c r="D158" t="s">
-        <v>272</v>
-      </c>
-      <c r="E158" t="s">
-        <v>273</v>
-      </c>
-      <c r="F158" t="s">
-        <v>274</v>
-      </c>
-      <c r="G158" t="s">
-        <v>200</v>
-      </c>
-      <c r="H158" t="s">
-        <v>127</v>
-      </c>
-      <c r="I158" t="s">
-        <v>88</v>
-      </c>
-      <c r="J158" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>275</v>
-      </c>
-      <c r="B159" t="s">
-        <v>276</v>
-      </c>
-      <c r="C159" t="s">
-        <v>277</v>
-      </c>
-      <c r="D159" t="s">
-        <v>258</v>
-      </c>
-      <c r="E159" t="s">
-        <v>278</v>
-      </c>
-      <c r="F159" t="s">
-        <v>279</v>
-      </c>
-      <c r="G159" t="s">
-        <v>225</v>
-      </c>
-      <c r="H159" t="s">
-        <v>115</v>
-      </c>
-      <c r="I159" t="s">
-        <v>88</v>
-      </c>
-      <c r="J159" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>280</v>
-      </c>
-      <c r="B160" t="s">
-        <v>281</v>
-      </c>
-      <c r="C160" t="s">
-        <v>282</v>
-      </c>
-      <c r="D160" t="s">
-        <v>40</v>
-      </c>
-      <c r="E160" t="s">
-        <v>218</v>
-      </c>
-      <c r="F160" t="s">
-        <v>259</v>
-      </c>
-      <c r="G160" t="s">
-        <v>40</v>
-      </c>
-      <c r="H160" t="s">
-        <v>40</v>
-      </c>
-      <c r="I160" t="s">
-        <v>40</v>
-      </c>
-      <c r="J160" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>283</v>
-      </c>
-      <c r="B161" t="s">
-        <v>284</v>
-      </c>
-      <c r="C161" t="s">
-        <v>271</v>
-      </c>
-      <c r="D161" t="s">
-        <v>78</v>
-      </c>
-      <c r="E161" t="s">
-        <v>285</v>
-      </c>
-      <c r="F161" t="s">
-        <v>286</v>
-      </c>
-      <c r="G161" t="s">
-        <v>287</v>
-      </c>
-      <c r="H161" t="s">
-        <v>288</v>
-      </c>
-      <c r="I161" t="s">
-        <v>83</v>
-      </c>
-      <c r="J161" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>289</v>
-      </c>
-      <c r="B162" t="s">
-        <v>290</v>
-      </c>
-      <c r="C162" t="s">
-        <v>271</v>
-      </c>
-      <c r="D162" t="s">
-        <v>291</v>
-      </c>
-      <c r="E162" t="s">
-        <v>292</v>
-      </c>
-      <c r="F162" t="s">
-        <v>293</v>
-      </c>
-      <c r="G162" t="s">
-        <v>294</v>
-      </c>
-      <c r="H162" t="s">
-        <v>295</v>
-      </c>
-      <c r="I162" t="s">
-        <v>57</v>
-      </c>
-      <c r="J162" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>269</v>
-      </c>
-      <c r="B163" t="s">
-        <v>270</v>
-      </c>
-      <c r="C163" t="s">
-        <v>271</v>
-      </c>
-      <c r="D163" t="s">
-        <v>272</v>
-      </c>
-      <c r="E163" t="s">
-        <v>273</v>
-      </c>
-      <c r="F163" t="s">
-        <v>274</v>
-      </c>
-      <c r="G163" t="s">
-        <v>200</v>
-      </c>
-      <c r="H163" t="s">
-        <v>127</v>
-      </c>
-      <c r="I163" t="s">
-        <v>88</v>
-      </c>
-      <c r="J163" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>275</v>
-      </c>
-      <c r="B164" t="s">
-        <v>276</v>
-      </c>
-      <c r="C164" t="s">
-        <v>277</v>
-      </c>
-      <c r="D164" t="s">
-        <v>258</v>
-      </c>
-      <c r="E164" t="s">
-        <v>278</v>
-      </c>
-      <c r="F164" t="s">
-        <v>279</v>
-      </c>
-      <c r="G164" t="s">
-        <v>225</v>
-      </c>
-      <c r="H164" t="s">
-        <v>115</v>
-      </c>
-      <c r="I164" t="s">
-        <v>88</v>
-      </c>
-      <c r="J164" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>280</v>
-      </c>
-      <c r="B165" t="s">
-        <v>281</v>
-      </c>
-      <c r="C165" t="s">
-        <v>282</v>
-      </c>
-      <c r="D165" t="s">
-        <v>40</v>
-      </c>
-      <c r="E165" t="s">
-        <v>218</v>
-      </c>
-      <c r="F165" t="s">
-        <v>259</v>
-      </c>
-      <c r="G165" t="s">
-        <v>40</v>
-      </c>
-      <c r="H165" t="s">
-        <v>40</v>
-      </c>
-      <c r="I165" t="s">
-        <v>40</v>
-      </c>
-      <c r="J165" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>283</v>
-      </c>
-      <c r="B166" t="s">
-        <v>284</v>
-      </c>
-      <c r="C166" t="s">
-        <v>271</v>
-      </c>
-      <c r="D166" t="s">
-        <v>78</v>
-      </c>
-      <c r="E166" t="s">
-        <v>285</v>
-      </c>
-      <c r="F166" t="s">
-        <v>286</v>
-      </c>
-      <c r="G166" t="s">
-        <v>287</v>
-      </c>
-      <c r="H166" t="s">
-        <v>288</v>
-      </c>
-      <c r="I166" t="s">
-        <v>83</v>
-      </c>
-      <c r="J166" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>289</v>
-      </c>
-      <c r="B167" t="s">
-        <v>290</v>
-      </c>
-      <c r="C167" t="s">
-        <v>271</v>
-      </c>
-      <c r="D167" t="s">
-        <v>291</v>
-      </c>
-      <c r="E167" t="s">
-        <v>292</v>
-      </c>
-      <c r="F167" t="s">
-        <v>293</v>
-      </c>
-      <c r="G167" t="s">
-        <v>294</v>
-      </c>
-      <c r="H167" t="s">
-        <v>295</v>
-      </c>
-      <c r="I167" t="s">
-        <v>57</v>
-      </c>
-      <c r="J167" t="s">
         <v>40</v>
       </c>
     </row>
